--- a/StructureDefinition-pcdch-molecularAnalysis.xlsx
+++ b/StructureDefinition-pcdch-molecularAnalysis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2021-11-30T11:37:05-07:00</t>
+    <t>2021-11-30T12:25:27-07:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
 </t>
   </si>
   <si>
-    <t>primary | metastatic | unknown | not-reported</t>
+    <t>primary | metastatic | unknown | not-reported (EWS, INRG)</t>
   </si>
   <si>
     <t>extensible</t>
@@ -259,7 +259,7 @@
     <t>pcdch-molecularAnalysis.sampleSource</t>
   </si>
   <si>
-    <t>blood | marrow |unknown | not-reported</t>
+    <t>blood | marrow |unknown | not-reported (ALL)</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis</t>
@@ -272,19 +272,19 @@
     <t>A cytogenetic molecular analysis</t>
   </si>
   <si>
-    <t>pcdch-molecularAnalysis.cytogeneticAnalysis.type</t>
-  </si>
-  <si>
-    <t>karyotyping | FISH | CMA | CGH | aCGH</t>
-  </si>
-  <si>
-    <t>http://example.org/fhir/pcdc/ValueSet/pcdch-cytogenetic-analysis-type-vs</t>
+    <t>pcdch-molecularAnalysis.cytogeneticAnalysis.method</t>
+  </si>
+  <si>
+    <t>karyotyping | FISH | CMA | CGH | aCGH (AML, EWS, ALL, GCT)</t>
+  </si>
+  <si>
+    <t>http://example.org/fhir/pcdc/ValueSet/pcdch-cytogenetic-analysis-method-vs</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.karyotypeStatus</t>
   </si>
   <si>
-    <t>normal | abnormal | unknown | not-reported</t>
+    <t>normal | abnormal | unknown | not-reported (ALL, GCT)</t>
   </si>
   <si>
     <t>http://example.org/fhir/pcdc/ValueSet/pcdch-karyotype-status-vs</t>
@@ -293,7 +293,7 @@
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.dnaIndex</t>
   </si>
   <si>
-    <t>hypodiploid | diploid | hyperdiploid | unknown | not-reported</t>
+    <t>hypodiploid | diploid | hyperdiploid | unknown | not-reported (INRG)</t>
   </si>
   <si>
     <t>http://example.org/fhir/pcdc/ValueSet/pcdch-dna-index-vs</t>
@@ -306,13 +306,13 @@
 </t>
   </si>
   <si>
-    <t>Numeric DNA Index</t>
+    <t>Numeric DNA Index (ALL)</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.cytodifferentiation</t>
   </si>
   <si>
-    <t>1 | 2 | 3 | unknown | not-reported</t>
+    <t>1 | 2 | 3 | unknown | not-reported (NRSTS)</t>
   </si>
   <si>
     <t>required</t>
@@ -324,19 +324,19 @@
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.chromosomeTotal</t>
   </si>
   <si>
-    <t>Number of chromosomes on karyotype</t>
+    <t>Number of chromosomes on karyotype (ALL, GCT)</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abberationTotal</t>
   </si>
   <si>
-    <t>Number of independent abberations on karyotype</t>
+    <t>Number of independent abberations on karyotype (AML, GCT)</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.metaphaseTotal</t>
   </si>
   <si>
-    <t>Number of cells in metaphase during karyotyping</t>
+    <t>Number of cells in metaphase during karyotyping (AML)</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.mitosesScore</t>
@@ -354,7 +354,7 @@
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abnormalityResult.status</t>
   </si>
   <si>
-    <t>positive | negative | not-done | unknown | not-reported</t>
+    <t>positive | negative | not-done | unknown | not-reported (AML, ALL, RMS)</t>
   </si>
   <si>
     <t>http://example.org/fhir/pcdc/ValueSet/pcdch-molecular-abnormality-result-status-vs</t>
@@ -363,7 +363,7 @@
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abnormalityResult.mutationType</t>
   </si>
   <si>
-    <t>somatic | germline/constitutional | unknown | not-reported</t>
+    <t>somatic | germline/constitutional | unknown | not-reported (INRG)</t>
   </si>
   <si>
     <t>http://example.org/fhir/pcdc/ValueSet/pcdch-mutation-type-vs</t>
@@ -372,7 +372,7 @@
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abnormalityResult.cytogeneticVariantType</t>
   </si>
   <si>
-    <t>translocation | inversion | mutation | SNV | CNV | rearrangement | deletion | amplification | other | unknown | not-reported</t>
+    <t>translocation | inversion | mutation | SNV | CNV | rearrangement | deletion | amplification | other | unknown | not-reported (AML, EWS, RMS, NRSTS, INRG, GCT, ALL)</t>
   </si>
   <si>
     <t>http://example.org/fhir/pcdc/ValueSet/pcdch-cytogenetic-variant-type-vs</t>
@@ -385,13 +385,13 @@
 </t>
   </si>
   <si>
-    <t>Valid ISCN string</t>
+    <t>Valid ISCN string (AML, ALL, GCT)</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abnormalityResult.translocationStatus</t>
   </si>
   <si>
-    <t>balanced | unbalanced| unknown | not-reported</t>
+    <t>balanced | unbalanced| unknown | not-reported (ALL)</t>
   </si>
   <si>
     <t>http://example.org/fhir/pcdc/ValueSet/pcdch-translocation-status-vs</t>
@@ -406,7 +406,7 @@
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abnormalityResult.geneFusion.gene1</t>
   </si>
   <si>
-    <t>Valid HGNC gene symbol</t>
+    <t>Valid HGNC gene symbol (AML, EWS, RMS, NRSTS, INRG, GCT, ALL)</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/uv/genomics-reporting/ValueSet/hgnc</t>
@@ -418,7 +418,7 @@
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abnormalityResult.repository</t>
   </si>
   <si>
-    <t>External repository which contains detailed report</t>
+    <t>External repository which contains detailed report (AML, ALL)</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abnormalityResult.repository.type</t>
@@ -470,13 +470,13 @@
     <t>A genotyping molecular analysis</t>
   </si>
   <si>
-    <t>pcdch-molecularAnalysis.genotypingAnalysis.type</t>
-  </si>
-  <si>
-    <t>NGS | DNA microarray | CE | GE | PCR | RT-PCR</t>
-  </si>
-  <si>
-    <t>http://example.org/fhir/pcdc/ValueSet/pcdch-genotyping-analysis-type-vs</t>
+    <t>pcdch-molecularAnalysis.genotypingAnalysis.method</t>
+  </si>
+  <si>
+    <t>NGS | DNA microarray | CE | GE | PCR | RT-PCR (AML, EWS, ALL, GCT)</t>
+  </si>
+  <si>
+    <t>http://example.org/fhir/pcdc/ValueSet/pcdch-genotyping-analysis-method-vs</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.genotypingAnalysis.abnormalityResult</t>
@@ -491,7 +491,7 @@
     <t>pcdch-molecularAnalysis.genotypingAnalysis.abnormalityResult.genotypingVariantType</t>
   </si>
   <si>
-    <t>substitution | deletion | duplication | insertion | inversion | frameshift | extension | other | unknown | not-reported</t>
+    <t>substitution | deletion | duplication | insertion | inversion | frameshift | extension | other | unknown | not-reported (AML, EWS, RMS, NRSTS, INRG, GCT, ALL)</t>
   </si>
   <si>
     <t>http://example.org/fhir/pcdc/ValueSet/pcdch-genotyping-variant-type-vs</t>
@@ -500,13 +500,13 @@
     <t>pcdch-molecularAnalysis.genotypingAnalysis.abnormalityResult.hgvs</t>
   </si>
   <si>
-    <t>Valid HGVS string</t>
+    <t>Valid HGVS string (AML, INRG, ALL)</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.genotypingAnalysis.abnormalityResult.allelicRatio</t>
   </si>
   <si>
-    <t>The percentage of reads that show SNV at a particular nucleotide position</t>
+    <t>The percentage of reads that show SNV at a particular nucleotide position (AML, INRG)</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.genotypingAnalysis.abnormalityResult.geneFusion</t>
@@ -841,7 +841,7 @@
     <col min="8" max="8" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.0625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.09375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="147.9140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-pcdch-molecularAnalysis.xlsx
+++ b/StructureDefinition-pcdch-molecularAnalysis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="177">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2021-11-30T12:25:27-07:00</t>
+    <t>2021-11-30T14:21:59-07:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -415,6 +415,15 @@
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abnormalityResult.geneFusion.gene2</t>
   </si>
   <si>
+    <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abnormalityResult.geneFusion.status</t>
+  </si>
+  <si>
+    <t>positive | negative | unknown (RMS)</t>
+  </si>
+  <si>
+    <t>http://example.org/fhir/pcdc/ValueSet/pcdch-fusion-status-vs</t>
+  </si>
+  <si>
     <t>pcdch-molecularAnalysis.cytogeneticAnalysis.abnormalityResult.repository</t>
   </si>
   <si>
@@ -516,6 +525,9 @@
   </si>
   <si>
     <t>pcdch-molecularAnalysis.genotypingAnalysis.abnormalityResult.geneFusion.gene2</t>
+  </si>
+  <si>
+    <t>pcdch-molecularAnalysis.genotypingAnalysis.abnormalityResult.geneFusion.status</t>
   </si>
   <si>
     <t>pcdch-molecularAnalysis.genotypingAnalysis.abnormalityResult.repository</t>
@@ -828,7 +840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ48"/>
+  <dimension ref="A1:AJ50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="79.59765625" customWidth="true" bestFit="true"/>
@@ -3163,7 +3175,7 @@
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>75</v>
@@ -3178,7 +3190,7 @@
         <v>70</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>133</v>
@@ -3211,13 +3223,11 @@
         <v>70</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>70</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="X24" s="2"/>
       <c r="Y24" t="s" s="2">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>70</v>
@@ -3238,7 +3248,7 @@
         <v>132</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3255,7 +3265,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -3263,7 +3273,7 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>75</v>
@@ -3278,13 +3288,13 @@
         <v>70</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -3311,11 +3321,13 @@
         <v>70</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="X25" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>70</v>
+      </c>
       <c r="Y25" t="s" s="2">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>70</v>
@@ -3333,10 +3345,10 @@
         <v>70</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3361,7 +3373,7 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>75</v>
@@ -3376,13 +3388,13 @@
         <v>70</v>
       </c>
       <c r="J26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="K26" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="L26" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -3409,13 +3421,11 @@
         <v>70</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>70</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="X26" s="2"/>
       <c r="Y26" t="s" s="2">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>70</v>
@@ -3436,7 +3446,7 @@
         <v>137</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3476,13 +3486,13 @@
         <v>70</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -3553,7 +3563,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -3579,10 +3589,10 @@
         <v>121</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -3633,7 +3643,7 @@
         <v>70</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>71</v>
@@ -3653,7 +3663,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -3679,10 +3689,10 @@
         <v>121</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -3733,7 +3743,7 @@
         <v>70</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>71</v>
@@ -3753,7 +3763,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -3779,10 +3789,10 @@
         <v>121</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -3833,7 +3843,7 @@
         <v>70</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>71</v>
@@ -3853,7 +3863,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -3876,13 +3886,13 @@
         <v>70</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -3933,7 +3943,7 @@
         <v>70</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>71</v>
@@ -3953,7 +3963,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -3961,7 +3971,7 @@
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>75</v>
@@ -3976,13 +3986,13 @@
         <v>70</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -4009,11 +4019,13 @@
         <v>70</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X32" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>70</v>
+      </c>
       <c r="Y32" t="s" s="2">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>70</v>
@@ -4031,10 +4043,10 @@
         <v>70</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4062,7 +4074,7 @@
         <v>75</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>70</v>
@@ -4074,13 +4086,13 @@
         <v>70</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -4107,13 +4119,11 @@
         <v>70</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>70</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="X33" s="2"/>
       <c r="Y33" t="s" s="2">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="Z33" t="s" s="2">
         <v>70</v>
@@ -4137,7 +4147,7 @@
         <v>75</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>70</v>
@@ -4151,7 +4161,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -4162,7 +4172,7 @@
         <v>75</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>70</v>
@@ -4174,13 +4184,13 @@
         <v>70</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -4207,11 +4217,13 @@
         <v>70</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X34" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>70</v>
+      </c>
       <c r="Y34" t="s" s="2">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>70</v>
@@ -4229,13 +4241,13 @@
         <v>70</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>70</v>
@@ -4249,7 +4261,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -4257,7 +4269,7 @@
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>75</v>
@@ -4275,10 +4287,10 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -4305,11 +4317,11 @@
         <v>70</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="X35" s="2"/>
       <c r="Y35" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>70</v>
@@ -4327,10 +4339,10 @@
         <v>70</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -4347,7 +4359,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -4373,10 +4385,10 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -4407,25 +4419,25 @@
       </c>
       <c r="X36" s="2"/>
       <c r="Y36" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AE36" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>71</v>
@@ -4468,7 +4480,7 @@
         <v>70</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>160</v>
@@ -4501,13 +4513,11 @@
         <v>70</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>70</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="X37" s="2"/>
       <c r="Y37" t="s" s="2">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>70</v>
@@ -4545,7 +4555,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -4568,13 +4578,13 @@
         <v>70</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -4625,7 +4635,7 @@
         <v>70</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>71</v>
@@ -4645,7 +4655,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -4668,13 +4678,13 @@
         <v>70</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -4725,7 +4735,7 @@
         <v>70</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>71</v>
@@ -4745,7 +4755,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -4753,7 +4763,7 @@
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>75</v>
@@ -4768,13 +4778,13 @@
         <v>70</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -4801,11 +4811,13 @@
         <v>70</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="X40" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>70</v>
+      </c>
       <c r="Y40" t="s" s="2">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>70</v>
@@ -4823,10 +4835,10 @@
         <v>70</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -4843,7 +4855,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -4921,7 +4933,7 @@
         <v>70</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>75</v>
@@ -4941,7 +4953,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -4949,7 +4961,7 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>75</v>
@@ -4964,13 +4976,13 @@
         <v>70</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -4997,13 +5009,11 @@
         <v>70</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>70</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="X42" s="2"/>
       <c r="Y42" t="s" s="2">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="Z42" t="s" s="2">
         <v>70</v>
@@ -5021,10 +5031,10 @@
         <v>70</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -5041,7 +5051,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -5067,10 +5077,10 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -5101,7 +5111,7 @@
       </c>
       <c r="X43" s="2"/>
       <c r="Y43" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Z43" t="s" s="2">
         <v>70</v>
@@ -5119,7 +5129,7 @@
         <v>70</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>75</v>
@@ -5139,7 +5149,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -5162,13 +5172,13 @@
         <v>70</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -5219,7 +5229,7 @@
         <v>70</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>71</v>
@@ -5239,7 +5249,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -5247,7 +5257,7 @@
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>75</v>
@@ -5262,13 +5272,13 @@
         <v>70</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -5295,13 +5305,11 @@
         <v>70</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>70</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="X45" s="2"/>
       <c r="Y45" t="s" s="2">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="Z45" t="s" s="2">
         <v>70</v>
@@ -5319,10 +5327,10 @@
         <v>70</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -5339,7 +5347,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -5362,13 +5370,13 @@
         <v>70</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -5419,7 +5427,7 @@
         <v>70</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>71</v>
@@ -5439,7 +5447,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -5465,10 +5473,10 @@
         <v>121</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -5519,7 +5527,7 @@
         <v>70</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>71</v>
@@ -5539,7 +5547,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -5565,10 +5573,10 @@
         <v>121</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -5619,7 +5627,7 @@
         <v>70</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>71</v>
@@ -5634,6 +5642,206 @@
         <v>70</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="P49" s="2"/>
+      <c r="Q49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="R49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="P50" s="2"/>
+      <c r="Q50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="R50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
         <v>70</v>
       </c>
     </row>
